--- a/bju_poi.xlsx
+++ b/bju_poi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BJU_Map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCEC264-4906-4F82-B9A8-E6B3EA0E407D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3D04A1-33CC-4797-BD30-69563111D038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>图书馆</t>
   </si>
   <si>
-    <t>宜游(学习)</t>
-  </si>
-  <si>
     <t>校区南部偏东</t>
   </si>
   <si>
@@ -769,6 +766,10 @@
   </si>
   <si>
     <t>12：00—21：00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜业(学习)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -896,7 +897,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1257,10 +1258,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="54" x14ac:dyDescent="0.15">
@@ -1301,7 +1302,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="81" x14ac:dyDescent="0.15">
@@ -1342,7 +1343,7 @@
         <v>20</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="94.5" x14ac:dyDescent="0.15">
@@ -1383,10 +1384,10 @@
         <v>20</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="94.5" x14ac:dyDescent="0.15">
@@ -1427,10 +1428,10 @@
         <v>20</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="175.5" x14ac:dyDescent="0.15">
@@ -1471,7 +1472,7 @@
         <v>20</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="94.5" x14ac:dyDescent="0.15">
@@ -1512,7 +1513,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="135" x14ac:dyDescent="0.15">
@@ -1553,7 +1554,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="108" x14ac:dyDescent="0.15">
@@ -1561,7 +1562,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1594,7 +1595,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="94.5" x14ac:dyDescent="0.15">
@@ -1635,7 +1636,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="67.5" x14ac:dyDescent="0.15">
@@ -1676,7 +1677,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="135" x14ac:dyDescent="0.15">
@@ -1684,13 +1685,13 @@
         <v>44</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E12" s="3">
         <v>116.288963</v>
@@ -1717,7 +1718,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="121.5" x14ac:dyDescent="0.15">
@@ -1731,7 +1732,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E13" s="2">
         <v>116.289141</v>
@@ -1758,7 +1759,7 @@
         <v>20</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="175.5" x14ac:dyDescent="0.15">
@@ -1799,7 +1800,7 @@
         <v>20</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="202.5" x14ac:dyDescent="0.15">
@@ -1809,11 +1810,11 @@
       <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E15" s="2">
         <v>116.28742099999999</v>
@@ -1825,7 +1826,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>18</v>
@@ -1840,21 +1841,21 @@
         <v>20</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="189" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="E16" s="3">
         <v>116.285758</v>
@@ -1866,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
@@ -1881,21 +1882,21 @@
         <v>20</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E17" s="2">
         <v>116.283006</v>
@@ -1907,16 +1908,16 @@
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>20</v>
@@ -1924,16 +1925,16 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E18" s="2">
         <v>116.284058</v>
@@ -1945,16 +1946,16 @@
         <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>20</v>
@@ -1962,16 +1963,16 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E19" s="2">
         <v>116.282957</v>
@@ -1983,16 +1984,16 @@
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>20</v>
@@ -2000,16 +2001,16 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E20" s="2">
         <v>116.284042</v>
@@ -2021,16 +2022,16 @@
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>20</v>
@@ -2038,16 +2039,16 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E21" s="2">
         <v>116.28288499999999</v>
@@ -2059,16 +2060,16 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>20</v>
@@ -2076,16 +2077,16 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E22" s="2">
         <v>116.288781</v>
@@ -2097,16 +2098,16 @@
         <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>20</v>
@@ -2114,16 +2115,16 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E23" s="2">
         <v>116.282985</v>
@@ -2135,16 +2136,16 @@
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
@@ -2152,16 +2153,16 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E24" s="2">
         <v>116.284007</v>
@@ -2173,16 +2174,16 @@
         <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>20</v>
@@ -2190,16 +2191,16 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E25" s="2">
         <v>116.283033</v>
@@ -2211,16 +2212,16 @@
         <v>16</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>20</v>
@@ -2228,16 +2229,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E26" s="2">
         <v>116.284066</v>
@@ -2249,16 +2250,16 @@
         <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>20</v>
@@ -2266,16 +2267,16 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E27" s="2">
         <v>116.288369</v>
@@ -2287,16 +2288,16 @@
         <v>16</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>20</v>
@@ -2304,16 +2305,16 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="3">
         <v>116.287544</v>
@@ -2325,7 +2326,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>18</v>
@@ -2334,7 +2335,7 @@
         <v>18</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>20</v>
@@ -2342,16 +2343,16 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="3">
         <v>116.288479</v>
@@ -2363,7 +2364,7 @@
         <v>16</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>18</v>
@@ -2372,7 +2373,7 @@
         <v>18</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>20</v>
@@ -2380,16 +2381,16 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="3">
         <v>116.288442</v>
@@ -2401,7 +2402,7 @@
         <v>16</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>18</v>
@@ -2410,7 +2411,7 @@
         <v>18</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>20</v>
@@ -2418,16 +2419,16 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3">
         <v>116.288442</v>
@@ -2439,7 +2440,7 @@
         <v>16</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>18</v>
@@ -2448,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>20</v>
@@ -2456,16 +2457,16 @@
     </row>
     <row r="32" spans="1:13" ht="94.5" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="E32" s="2">
         <v>116.28717399999999</v>
@@ -2477,10 +2478,10 @@
         <v>16</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>18</v>
@@ -2492,21 +2493,21 @@
         <v>20</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="E33" s="3">
         <v>116.287068</v>
@@ -2518,7 +2519,7 @@
         <v>16</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>18</v>
@@ -2535,16 +2536,16 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E34" s="2">
         <v>116.28554099999999</v>
@@ -2556,7 +2557,7 @@
         <v>16</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>18</v>
@@ -2573,16 +2574,16 @@
     </row>
     <row r="35" spans="1:13" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E35" s="3">
         <v>116.284013</v>
@@ -2594,7 +2595,7 @@
         <v>16</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>18</v>
@@ -2609,21 +2610,21 @@
         <v>20</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="E36" s="2">
         <v>116.288704</v>
@@ -2635,36 +2636,36 @@
         <v>16</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="M36" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" s="3">
         <v>116.288983</v>
@@ -2687,13 +2688,13 @@
     </row>
     <row r="38" spans="1:13" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3">
@@ -2715,21 +2716,21 @@
         <v>20</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E39" s="3">
         <v>116.28335237503001</v>
@@ -2741,7 +2742,7 @@
         <v>16</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>18</v>
@@ -2753,18 +2754,18 @@
         <v>19</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2">
@@ -2786,16 +2787,16 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41" s="2">
         <v>116.284278</v>
@@ -2807,7 +2808,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>18</v>
@@ -2824,16 +2825,16 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
         <v>127</v>
-      </c>
-      <c r="B42" t="s">
-        <v>128</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E42" s="3">
         <v>116.286041289567</v>
@@ -2851,18 +2852,18 @@
         <v>19</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2">
@@ -2884,13 +2885,13 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3">
@@ -2906,7 +2907,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>20</v>
@@ -2914,13 +2915,13 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2">
@@ -2944,10 +2945,10 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>27</v>
@@ -2974,10 +2975,10 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>27</v>
@@ -3004,13 +3005,13 @@
     </row>
     <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3">
@@ -3029,18 +3030,18 @@
         <v>19</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="27" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2">
@@ -3054,7 +3055,7 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="3" t="s">
@@ -3064,18 +3065,18 @@
         <v>20</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" t="s">
         <v>147</v>
       </c>
-      <c r="B50" t="s">
-        <v>148</v>
-      </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E50">
         <v>116.28818437456999</v>
@@ -3090,18 +3091,18 @@
         <v>19</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" t="s">
         <v>149</v>
       </c>
-      <c r="B51" t="s">
-        <v>150</v>
-      </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E51">
         <v>116.28581598401</v>
@@ -3116,18 +3117,18 @@
         <v>19</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" t="s">
         <v>151</v>
       </c>
-      <c r="B52" t="s">
-        <v>152</v>
-      </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E52">
         <v>116.28564298152899</v>
@@ -3142,18 +3143,18 @@
         <v>19</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" t="s">
         <v>153</v>
       </c>
-      <c r="B53" t="s">
-        <v>154</v>
-      </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E53">
         <v>116.288550496101</v>
@@ -3168,18 +3169,18 @@
         <v>19</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E54">
         <v>116.288710087537</v>
@@ -3194,18 +3195,18 @@
         <v>19</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E55">
         <v>116.287191957235</v>
@@ -3220,18 +3221,18 @@
         <v>19</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E56">
         <v>116.28720134496599</v>
@@ -3246,18 +3247,18 @@
         <v>19</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E57">
         <v>116.283380538225</v>
@@ -3272,18 +3273,18 @@
         <v>19</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58">
         <v>116.28597959875999</v>
@@ -3298,18 +3299,18 @@
         <v>19</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E59">
         <v>116.286461055278</v>
@@ -3324,18 +3325,18 @@
         <v>19</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E60">
         <v>116.28859609365399</v>
@@ -3350,18 +3351,18 @@
         <v>19</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E61">
         <v>116.28860682249</v>
@@ -3376,18 +3377,18 @@
         <v>19</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E62">
         <v>116.288280934095</v>
@@ -3402,18 +3403,18 @@
         <v>19</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E63">
         <v>116.28859609365399</v>
@@ -3428,18 +3429,18 @@
         <v>19</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" t="s">
         <v>165</v>
       </c>
-      <c r="B64" t="s">
-        <v>166</v>
-      </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E64">
         <v>116.284059137105</v>
@@ -3451,21 +3452,21 @@
         <v>16</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" t="s">
         <v>167</v>
       </c>
-      <c r="B65" t="s">
-        <v>168</v>
-      </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E65">
         <v>116.286041289567</v>
@@ -3477,21 +3478,21 @@
         <v>16</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" t="s">
         <v>169</v>
       </c>
-      <c r="B66" t="s">
-        <v>170</v>
-      </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E66">
         <v>116.286119</v>
@@ -3503,18 +3504,18 @@
         <v>16</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" t="s">
         <v>171</v>
-      </c>
-      <c r="B67" t="s">
-        <v>172</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>27</v>
@@ -3537,10 +3538,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" t="s">
         <v>173</v>
-      </c>
-      <c r="B68" t="s">
-        <v>174</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>27</v>
@@ -3563,10 +3564,10 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" t="s">
         <v>175</v>
-      </c>
-      <c r="B69" t="s">
-        <v>176</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>27</v>
@@ -3589,13 +3590,13 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" t="s">
         <v>177</v>
       </c>
-      <c r="B70" t="s">
-        <v>178</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E70">
         <v>116.287402</v>
@@ -3615,13 +3616,13 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" t="s">
         <v>179</v>
       </c>
-      <c r="B71" t="s">
-        <v>180</v>
-      </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E71">
         <v>116.28330141305899</v>
@@ -3636,18 +3637,18 @@
         <v>19</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" t="s">
         <v>181</v>
       </c>
-      <c r="B72" t="s">
-        <v>182</v>
-      </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E72">
         <v>116.285109221935</v>
@@ -3662,18 +3663,18 @@
         <v>19</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" t="s">
         <v>183</v>
       </c>
-      <c r="B73" t="s">
-        <v>184</v>
-      </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E73">
         <v>116.28219500183999</v>
@@ -3688,18 +3689,18 @@
         <v>19</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B74" t="s">
         <v>185</v>
       </c>
-      <c r="B74" t="s">
-        <v>186</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E74">
         <v>116.290566176176</v>
@@ -3714,7 +3715,7 @@
         <v>19</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.15">
